--- a/docs/latexLNNS/ALT_Text_711623_211.xlsx
+++ b/docs/latexLNNS/ALT_Text_711623_211.xlsx
@@ -95,53 +95,15 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pareto_N400.pdf</t>
+          <t>comparison_row_N200.png</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>The chart compares the average delay time in seconds against the fleet distance in kilometers for six different methods. Lower values on both axes are better, meaning shorter delays and shorter distances. The methods are shown as colored shapes: blue circles for K-medoids with TSP, orange circles for Sectorial, green squares for CVRPTW-zones, purple downward triangles for SetCover-grid, red upward triangles for SetCover-child, and brown diamonds for ALNS. Most methods cluster around 450 to 600 kilometers with delays ranging from about 0.1 to 100 seconds. The SetCover-child method stands out with the shortest delay near 0.1 seconds but the longest distance around 660 kilometers. A note highlights that K-medoids and Sectorial results are nearly the same, differing by only 1 kilometer, 0.22 percent in distance, and 0.03 seconds in delay. This chart helps show the trade-offs between distance traveled and delay time for different routing methods.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>comparison_row_N200.png</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Three side-by-side maps compare different bus route planning methods for a city area, each showing routes as colored lines connecting stops marked by dots. A red square near the center marks a common starting point for all routes. The left map uses a clustering method with 10 buses and 10 routes, showing routes grouped by color in distinct areas. The middle map uses a grid-based set cover method with 11 buses and routes, displaying more evenly spread routes covering the area. The right map uses a destroy-repair search method with 10 buses and routes, showing routes that appear more intertwined and overlapping. This comparison highlights how different planning methods affect the number, layout, and coverage of bus routes in the same city area.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Table1_benchmarksRuns.png</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>The table compares six strategies for fleet distance in kilometers and latency in seconds across four density categories: 50, 100, 200, and 400 children. The strategies are K-medoids plus TSP, Sectorial, CVRPTW zonal, Set Cover per-child, Set Cover grid, and ALNS. For fleet distance, ALNS consistently shows the lowest values at 50, 100, and 200 km, marked in bold, indicating it achieves the shortest total fleet distance among full-coverage methods. Latency values vary widely; Set Cover per-child has the lowest latency across all distances, while CVRPTW zonal has the highest latency consistently at 100 seconds. The note explains that CVRPTW zonal may leave about 1% of students unserved, so its distance results are not fully comparable. This table highlights trade-offs between minimizing fleet distance and latency for different routing strategies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>scalability.pdf</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>The chart compares the average time delay in seconds for six different methods as the number of students increases from 50 to 400. The horizontal axis shows the number of students, and the vertical axis shows the mean latency on a logarithmic scale. The red line with triangles, representing the SetCover-child method, consistently has the lowest latency, increasing slowly from about 0.01 to 0.1 seconds. The purple line with downward triangles, for SetCover-grid, starts around 0.3 seconds and rises to about 30 seconds. The blue line with circles (K-medoids plus TSP) and the brown line with diamonds (ALNS) both start near 10 seconds and increase to around 100 seconds. The orange line with circles (Sectorial) is close to the blue and brown lines. The green line with squares (CVRPTW-zones) remains nearly constant at about 100 seconds regardless of the number of students. This chart highlights that SetCover-child is the fastest method, especially as the number of students grows, while CVRPTW-zones is the slowest and least affected by student count.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-</row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/latexLNNS/ALT_Text_711623_211.xlsx
+++ b/docs/latexLNNS/ALT_Text_711623_211.xlsx
@@ -104,6 +104,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Table1_benchmarksRuns.png</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>The table reports total fleet distance in kilometres (mean plus or minus standard deviation over 11 seeds) and mean latency in seconds for six routing strategies at four student densities: 50, 100, 200 and 400 students. The strategies are K-medoids plus TSP, Sectorial, zonal CVRPTW, Set Cover per-child, Set Cover grid, and ALNS. ALNS has the shortest fleet distance at all four densities, shown in bold, from 98 kilometres at 50 students to 428 kilometres at 400 students. Set Cover per-child is the fastest at every density, from 0.02 to 0.16 seconds, while the zonal CVRPTW is pinned at 100 seconds throughout. A footnote records that the zonal CVRPTW may leave about 1 percent of students unserved when its duration limit binds, so its distances are not strictly comparable with the full-coverage methods.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/latexLNNS/ALT_Text_711623_211.xlsx
+++ b/docs/latexLNNS/ALT_Text_711623_211.xlsx
@@ -95,22 +95,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>comparison_row_N200.png</t>
+          <t>pareto_N400.pdf</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Three side-by-side maps compare different bus route planning methods for a city area, each showing routes as colored lines connecting stops marked by dots. A red square near the center marks a common starting point for all routes. The left map uses a clustering method with 10 buses and 10 routes, showing routes grouped by color in distinct areas. The middle map uses a grid-based set cover method with 11 buses and routes, displaying more evenly spread routes covering the area. The right map uses a destroy-repair search method with 10 buses and routes, showing routes that appear more intertwined and overlapping. This comparison highlights how different planning methods affect the number, layout, and coverage of bus routes in the same city area.</t>
+          <t>The chart compares the average delay time in seconds against the fleet distance in kilometers for six different methods. Lower values on both axes are better, meaning shorter delays and shorter distances. The methods are shown as colored shapes: blue circles for K-medoids with TSP, orange circles for Sectorial, green squares for CVRPTW-zones, purple downward triangles for SetCover-grid, red upward triangles for SetCover-child, and brown diamonds for ALNS. Most methods cluster around 450 to 600 kilometers with delays ranging from about 0.1 to 100 seconds. The SetCover-child method stands out with the shortest delay near 0.1 seconds but the longest distance around 660 kilometers. A note highlights that K-medoids and Sectorial results are nearly the same, differing by only 1 kilometer, 0.22 percent in distance, and 0.03 seconds in delay. This chart helps show the trade-offs between distance traveled and delay time for different routing methods.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
+          <t>comparison_row_N200.png</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Three side-by-side maps compare different bus route planning methods for a city area, each showing routes as colored lines connecting stops marked by dots. A red square near the center marks a common starting point for all routes. The left map uses a clustering method with 10 buses and 10 routes, showing routes grouped by color in distinct areas. The middle map uses a grid-based set cover method with 11 buses and routes, displaying more evenly spread routes covering the area. The right map uses a destroy-repair search method with 10 buses and routes, showing routes that appear more intertwined and overlapping. This comparison highlights how different planning methods affect the number, layout, and coverage of bus routes in the same city area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
           <t>Table1_benchmarksRuns.png</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>The table reports total fleet distance in kilometres (mean plus or minus standard deviation over 11 seeds) and mean latency in seconds for six routing strategies at four student densities: 50, 100, 200 and 400 students. The strategies are K-medoids plus TSP, Sectorial, zonal CVRPTW, Set Cover per-child, Set Cover grid, and ALNS. ALNS has the shortest fleet distance at all four densities, shown in bold, from 98 kilometres at 50 students to 428 kilometres at 400 students. Set Cover per-child is the fastest at every density, from 0.02 to 0.16 seconds, while the zonal CVRPTW is pinned at 100 seconds throughout. A footnote records that the zonal CVRPTW may leave about 1 percent of students unserved when its duration limit binds, so its distances are not strictly comparable with the full-coverage methods.</t>
         </is>
